--- a/MODULE 1 - TRAFFIC (AKSHIT)FINAL.xlsx
+++ b/MODULE 1 - TRAFFIC (AKSHIT)FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akshi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75C01E36-733B-4FFE-BCFC-A41F82A53F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72799D27-2C4E-49A8-9CAC-7D78C51D45A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -467,6 +467,13 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
@@ -520,13 +527,13 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="-0.249977111117893"/>
+          <bgColor theme="8" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
@@ -534,21 +541,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="-0.249977111117893"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.59999389629810485"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -561,6 +561,54 @@
       <font>
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -878,28 +926,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59999389629810485"/>
+          <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF0070C0"/>
+          <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.39997558519241921"/>
+          <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.39997558519241921"/>
+          <bgColor theme="8" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
     </dxf>
@@ -912,54 +960,6 @@
       <font>
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -2001,7 +2001,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2014,14 +2014,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="2400" b="1" baseline="0">
+              <a:rPr lang="en-US" sz="2800" b="1" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t> TRAFFIC CONDITION DISTRIBUTION</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" sz="2400" b="1">
+            <a:endParaRPr lang="en-US" sz="2800" b="1">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -2050,7 +2050,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3831,7 +3831,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="bg1"/>
                 </a:solidFill>
@@ -3841,7 +3841,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="2800"/>
               <a:t>AVERAGE TRAVEL TIME BY LOCATION</a:t>
             </a:r>
           </a:p>
@@ -3851,8 +3851,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.34638686131386864"/>
-          <c:y val="1.6862656319811563E-2"/>
+          <c:x val="0.25161882847385986"/>
+          <c:y val="1.6862602843932272E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -3868,7 +3868,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -4640,7 +4640,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="bg1"/>
                 </a:solidFill>
@@ -7982,7 +7982,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2760" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="bg1"/>
                 </a:solidFill>
@@ -7992,7 +7992,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US">
+              <a:rPr lang="en-US" sz="2800">
                 <a:solidFill>
                   <a:schemeClr val="bg1"/>
                 </a:solidFill>
@@ -8023,7 +8023,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2760" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="2800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -11077,7 +11077,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5CD1-4329-A000-A7ACDDB3C686}"/>
+              <c16:uniqueId val="{00000028-C27C-4F54-B93E-0782087E1B1E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11209,7 +11209,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5CD1-4329-A000-A7ACDDB3C686}"/>
+              <c16:uniqueId val="{00000029-C27C-4F54-B93E-0782087E1B1E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11344,7 +11344,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DAAF-4007-B311-AC081BAAE198}"/>
+              <c16:uniqueId val="{0000002A-C27C-4F54-B93E-0782087E1B1E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11479,7 +11479,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-DAAF-4007-B311-AC081BAAE198}"/>
+              <c16:uniqueId val="{0000002B-C27C-4F54-B93E-0782087E1B1E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11619,10 +11619,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.8772553972046031"/>
-          <c:y val="0.34786177064421331"/>
-          <c:w val="0.12274467224822513"/>
-          <c:h val="0.26310412129592492"/>
+          <c:x val="0.88340917165251065"/>
+          <c:y val="0.34974511302893219"/>
+          <c:w val="0.11659082834748959"/>
+          <c:h val="0.24994865186110121"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -15013,15 +15013,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>51</xdr:col>
-      <xdr:colOff>239711</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>119866</xdr:rowOff>
+      <xdr:colOff>217941</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>98094</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>55</xdr:col>
-      <xdr:colOff>488841</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>179842</xdr:rowOff>
+      <xdr:colOff>467071</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -15057,8 +15057,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="30920237" y="4471287"/>
-              <a:ext cx="2655446" cy="1684239"/>
+              <a:off x="31307541" y="4474151"/>
+              <a:ext cx="2687530" cy="1600078"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15091,15 +15091,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>51</xdr:col>
-      <xdr:colOff>244175</xdr:colOff>
+      <xdr:colOff>222402</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>14983</xdr:rowOff>
+      <xdr:rowOff>36755</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>55</xdr:col>
-      <xdr:colOff>485474</xdr:colOff>
+      <xdr:colOff>463701</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -15135,8 +15135,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="30924701" y="1639246"/>
-              <a:ext cx="2647615" cy="2712176"/>
+              <a:off x="31312002" y="1604298"/>
+              <a:ext cx="2679699" cy="2749988"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15169,15 +15169,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>275904</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>41627</xdr:rowOff>
+      <xdr:colOff>297676</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>106941</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>148903</xdr:colOff>
+      <xdr:colOff>170675</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>150725</xdr:rowOff>
+      <xdr:rowOff>41868</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -15192,8 +15192,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3332278" y="3910242"/>
-          <a:ext cx="4151922" cy="477538"/>
+          <a:off x="3345676" y="3612141"/>
+          <a:ext cx="4140199" cy="457441"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15252,9 +15252,21 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> MODAL CONGESTION</a:t>
+            <a:t> MODAL </a:t>
           </a:r>
-          <a:endParaRPr lang="en-IN" sz="2400" b="1">
+          <a:r>
+            <a:rPr lang="en-IN" sz="2800" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CONGESTION</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="2800" b="1">
             <a:solidFill>
               <a:schemeClr val="bg2"/>
             </a:solidFill>
@@ -15271,15 +15283,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>51</xdr:col>
-      <xdr:colOff>244863</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>109035</xdr:rowOff>
+      <xdr:colOff>218676</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>54836</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>55</xdr:col>
-      <xdr:colOff>477119</xdr:colOff>
+      <xdr:colOff>474251</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>164122</xdr:rowOff>
+      <xdr:rowOff>170518</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -15315,8 +15327,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="30925389" y="6265193"/>
-              <a:ext cx="2638572" cy="1859824"/>
+              <a:off x="31308276" y="6172607"/>
+              <a:ext cx="2693975" cy="1683225"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15349,15 +15361,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>51</xdr:col>
-      <xdr:colOff>239401</xdr:colOff>
+      <xdr:colOff>229200</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>93785</xdr:rowOff>
+      <xdr:rowOff>115557</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>55</xdr:col>
-      <xdr:colOff>465396</xdr:colOff>
+      <xdr:colOff>484909</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>93784</xdr:rowOff>
+      <xdr:rowOff>87086</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -15393,8 +15405,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="30919927" y="8235153"/>
-              <a:ext cx="2632311" cy="2346157"/>
+              <a:off x="31318800" y="7975043"/>
+              <a:ext cx="2694109" cy="2235757"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15898,13 +15910,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>175290</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1118</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>610591</xdr:colOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>112290</xdr:rowOff>
     </xdr:to>
@@ -15921,8 +15933,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18928378" y="1644684"/>
-          <a:ext cx="5495334" cy="1053938"/>
+          <a:off x="18897601" y="1568661"/>
+          <a:ext cx="5486400" cy="1003800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15990,13 +16002,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>2481</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>794</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>51</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
@@ -16013,8 +16025,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24996081" y="1646714"/>
-          <a:ext cx="6093519" cy="1058386"/>
+          <a:off x="24993601" y="1568337"/>
+          <a:ext cx="6096000" cy="1021374"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18566,152 +18578,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D82956D7-CE54-4D75-89A6-A0F85077C57C}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
-  <location ref="G1:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="16">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="11">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="24" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9FE88A9E-E09F-4F32-9C58-D4E09152204D}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E1:F5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -18794,38 +18660,38 @@
     <dataField name="Count of Road_Type" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="26">
+    <format dxfId="17">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="15">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="13">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="12">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="10">
       <pivotArea dataOnly="0" grandRow="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="9">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -18841,643 +18707,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F7139294-D4CC-44FB-AA38-BBFA4880655D}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="K1:L7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="38">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="33">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="32">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea field="5" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="28">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE6721BD-F1E2-4513-BB51-352F6128DB18}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="A1:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Speed_kmh" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="13">
-    <format dxfId="51">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="49">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="48">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="47">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="46">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="41">
-      <pivotArea field="1" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="1">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="40">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="39">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42347EC-AE40-4424-BE0A-30218EA67FD0}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="I1:J6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="61">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="60">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="59">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="58">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="57">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="56">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="55">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="54">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="53">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="52">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{612073D7-073C-47F8-A4EC-D6FF2A56D407}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="C1:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Vehicle_Type" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="70">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="69">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="68">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="67">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="66">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="65">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="64">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="63">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="62">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="6">
-    <chartFormat chart="12" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="25">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="26">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="27">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="28">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="29">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1352BCF6-A19A-45AA-9E04-FF9B6EA3CDB4}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="M1:S11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
@@ -19588,65 +18818,65 @@
     <dataField name="Average of Speed_kmh" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
   </dataFields>
   <formats count="17">
-    <format dxfId="87">
+    <format dxfId="34">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="33">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="85">
+    <format dxfId="32">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="84">
+    <format dxfId="31">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="83">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="81">
+    <format dxfId="28">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="80">
+    <format dxfId="27">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="26">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="25">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="77">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="75">
+    <format dxfId="22">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="20">
       <pivotArea field="1" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -19656,14 +18886,14 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="19">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="18">
       <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
     </format>
   </formats>
@@ -19778,6 +19008,788 @@
           </reference>
           <reference field="5" count="1" selected="0">
             <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F7139294-D4CC-44FB-AA38-BBFA4880655D}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="K1:L7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="46">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="41">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="40">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea field="5" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="36">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE6721BD-F1E2-4513-BB51-352F6128DB18}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="A1:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Speed_kmh" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="13">
+    <format dxfId="59">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="55">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="53">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="49">
+      <pivotArea field="1" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="48">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42347EC-AE40-4424-BE0A-30218EA67FD0}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="I1:J6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="69">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="68">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="67">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="66">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="65">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="64">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="63">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="61">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{612073D7-073C-47F8-A4EC-D6FF2A56D407}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="C1:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Vehicle_Type" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="78">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="77">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="76">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="75">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="74">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="73">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="72">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="71">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="70">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="6">
+    <chartFormat chart="12" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="25">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="26">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="27">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="28">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="29">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D82956D7-CE54-4D75-89A6-A0F85077C57C}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="G1:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="87">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="86">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="85">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="84">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="83">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="82">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="81">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="80">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="79">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="24" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>

--- a/MODULE 1 - TRAFFIC (AKSHIT)FINAL.xlsx
+++ b/MODULE 1 - TRAFFIC (AKSHIT)FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akshi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72799D27-2C4E-49A8-9CAC-7D78C51D45A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C59863A-F6FC-4A68-BC96-DD3FEC0659C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -467,13 +467,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
@@ -527,13 +520,13 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59999389629810485"/>
+          <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
@@ -541,14 +534,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.39997558519241921"/>
+          <bgColor theme="8" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.39997558519241921"/>
+          <bgColor theme="8" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
     </dxf>
@@ -561,54 +561,6 @@
       <font>
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -926,28 +878,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="-0.249977111117893"/>
+          <bgColor theme="8" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="-0.249977111117893"/>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="-0.249977111117893"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.59999389629810485"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -960,6 +912,54 @@
       <font>
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -15729,16 +15729,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>610593</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>173291</xdr:rowOff>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>22764</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>20891</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>110291</xdr:rowOff>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>21771</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>153834</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -15753,8 +15753,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipH="1" flipV="1">
-          <a:off x="6716521" y="1642685"/>
-          <a:ext cx="5495336" cy="1053938"/>
+          <a:off x="35379564" y="4048605"/>
+          <a:ext cx="5485407" cy="1003800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15806,10 +15806,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-IN" sz="4000" b="1"/>
-            <a:t>AVERAGE SPEED </a:t>
-          </a:r>
+          <a:endParaRPr lang="en-IN" sz="4000" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -16091,6 +16088,121 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>21772</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>21768</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>137140</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35FDC6E3-74E6-F0AD-D998-5F7869F5E7A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6727372" y="1589311"/>
+          <a:ext cx="5464628" cy="1008000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="44450" dist="27940" dir="5400000" algn="ctr">
+            <a:srgbClr val="000000">
+              <a:alpha val="32000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="0"/>
+          </a:camera>
+          <a:lightRig rig="balanced" dir="t">
+            <a:rot lat="0" lon="0" rev="8700000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="190500" h="38100"/>
+        </a:sp3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="4000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>AVERAGE SPEED</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="4000" b="1">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -18578,6 +18690,152 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D82956D7-CE54-4D75-89A6-A0F85077C57C}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="G1:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="16">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="24" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9FE88A9E-E09F-4F32-9C58-D4E09152204D}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E1:F5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -18660,38 +18918,38 @@
     <dataField name="Count of Road_Type" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="17">
+    <format dxfId="26">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="24">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="22">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="21">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="19">
       <pivotArea dataOnly="0" grandRow="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="18">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -18707,7 +18965,643 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F7139294-D4CC-44FB-AA38-BBFA4880655D}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="K1:L7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="38">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea field="5" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE6721BD-F1E2-4513-BB51-352F6128DB18}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="A1:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Speed_kmh" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="13">
+    <format dxfId="51">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="49">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea field="1" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="40">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="9" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42347EC-AE40-4424-BE0A-30218EA67FD0}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="I1:J6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="61">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="59">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="57">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="55">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="53">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{612073D7-073C-47F8-A4EC-D6FF2A56D407}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="C1:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Vehicle_Type" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="70">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="69">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="68">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="67">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="66">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="65">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="64">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="6">
+    <chartFormat chart="12" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="25">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="26">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="27">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="28">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="29">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1352BCF6-A19A-45AA-9E04-FF9B6EA3CDB4}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="M1:S11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
@@ -18818,65 +19712,65 @@
     <dataField name="Average of Speed_kmh" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
   </dataFields>
   <formats count="17">
-    <format dxfId="34">
+    <format dxfId="87">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="86">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="85">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="84">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="83">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="82">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="81">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="80">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="79">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="78">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="77">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="75">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="73">
       <pivotArea field="1" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -18886,14 +19780,14 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="72">
       <pivotArea dataOnly="0" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="71">
       <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
     </format>
   </formats>
@@ -19008,788 +19902,6 @@
           </reference>
           <reference field="5" count="1" selected="0">
             <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F7139294-D4CC-44FB-AA38-BBFA4880655D}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="K1:L7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="46">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="41">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="40">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="39">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea field="5" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="36">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE6721BD-F1E2-4513-BB51-352F6128DB18}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="A1:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Speed_kmh" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="13">
-    <format dxfId="59">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="58">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="57">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="56">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="55">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="54">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="53">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="52">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="51">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="49">
-      <pivotArea field="1" dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="1">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="48">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="9" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42347EC-AE40-4424-BE0A-30218EA67FD0}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="I1:J6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="69">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="68">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="67">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="66">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="65">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="64">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="63">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="62">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="61">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="60">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{612073D7-073C-47F8-A4EC-D6FF2A56D407}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="C1:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Vehicle_Type" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="78">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="77">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="76">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="75">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="74">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="73">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="72">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="71">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="70">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="6">
-    <chartFormat chart="12" format="24" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="25">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="26">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="27">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="28">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="29">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D82956D7-CE54-4D75-89A6-A0F85077C57C}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
-  <location ref="G1:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Travel_Time_mins" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="87">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="86">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="85">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="84">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="83">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="82">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="81">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="80">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="79">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="24" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
           </reference>
         </references>
       </pivotArea>

--- a/MODULE 1 - TRAFFIC (AKSHIT)FINAL.xlsx
+++ b/MODULE 1 - TRAFFIC (AKSHIT)FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akshi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C59863A-F6FC-4A68-BC96-DD3FEC0659C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5960DB91-28DA-44B7-9034-7B45F095CD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16091,13 +16091,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>21772</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>21768</xdr:rowOff>
+      <xdr:colOff>2042</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>181817</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>608782</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>137140</xdr:rowOff>
     </xdr:to>
@@ -16114,8 +16114,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6727372" y="1589311"/>
-          <a:ext cx="5464628" cy="1008000"/>
+          <a:off x="6698653" y="1652702"/>
+          <a:ext cx="5477003" cy="1072787"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
